--- a/artfynd/A 35068-2025 artfynd.xlsx
+++ b/artfynd/A 35068-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127721727</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>127722108</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127721543</v>
+        <v>127721853</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,6 +1092,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,7 +1126,7 @@
         <v>127722196</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1238,7 @@
         <v>127722396</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1350,7 @@
         <v>127721889</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35068-2025 artfynd.xlsx
+++ b/artfynd/A 35068-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127721853</v>
+        <v>127721543</v>
       </c>
       <c r="B5" t="n">
         <v>79020</v>
@@ -1092,11 +1092,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 35068-2025 artfynd.xlsx
+++ b/artfynd/A 35068-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127721543</v>
+        <v>127721853</v>
       </c>
       <c r="B5" t="n">
         <v>79020</v>
@@ -1092,6 +1092,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 35068-2025 artfynd.xlsx
+++ b/artfynd/A 35068-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127721727</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>127722108</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>127721853</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>127722196</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>127722396</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>127721889</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35068-2025 artfynd.xlsx
+++ b/artfynd/A 35068-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127721727</v>
       </c>
       <c r="B2" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>127722108</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127721853</v>
+        <v>127721543</v>
       </c>
       <c r="B5" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,11 +1092,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,7 +1121,7 @@
         <v>127722196</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1233,7 @@
         <v>127722396</v>
       </c>
       <c r="B7" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1345,7 @@
         <v>127721889</v>
       </c>
       <c r="B8" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35068-2025 artfynd.xlsx
+++ b/artfynd/A 35068-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127721543</v>
+        <v>127721853</v>
       </c>
       <c r="B5" t="n">
         <v>79029</v>
@@ -1092,6 +1092,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 35068-2025 artfynd.xlsx
+++ b/artfynd/A 35068-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127721727</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>127722108</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>127721853</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>127722196</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>127722396</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>127721889</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35068-2025 artfynd.xlsx
+++ b/artfynd/A 35068-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127721727</v>
       </c>
       <c r="B2" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>127722108</v>
       </c>
       <c r="B3" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>127721853</v>
       </c>
       <c r="B5" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>127722196</v>
       </c>
       <c r="B6" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>127722396</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>127721889</v>
       </c>
       <c r="B8" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35068-2025 artfynd.xlsx
+++ b/artfynd/A 35068-2025 artfynd.xlsx
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127721727</v>
+        <v>127721543</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465163</v>
+        <v>465222</v>
       </c>
       <c r="R2" t="n">
-        <v>6783960</v>
+        <v>6783974</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +756,6 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt med garn i anmälan och äldre tallar  3 bilder</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,14 +782,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127722108</v>
+        <v>127721727</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465236</v>
+        <v>465163</v>
       </c>
       <c r="R3" t="n">
-        <v>6783887</v>
+        <v>6783960</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +867,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2 bild grov tall med garn</t>
+          <t>Rikligt med garn i anmälan och äldre tallar  3 bilder</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127721821</v>
+        <v>127721889</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465217</v>
+        <v>465233</v>
       </c>
       <c r="R4" t="n">
-        <v>6783956</v>
+        <v>6783962</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>1 bild på låga samt garn i gran</t>
+          <t>1 bild på sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,14 +1006,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127721853</v>
+        <v>127722108</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1046,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465222</v>
+        <v>465236</v>
       </c>
       <c r="R5" t="n">
-        <v>6783974</v>
+        <v>6783887</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>2 bild grov tall med garn</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,11 +1121,11 @@
         <v>127722196</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1238,11 +1233,11 @@
         <v>127722396</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1347,32 +1342,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127721889</v>
+        <v>127721821</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>8455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465233</v>
+        <v>465217</v>
       </c>
       <c r="R8" t="n">
-        <v>6783962</v>
+        <v>6783956</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1427,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 bild på sälg</t>
+          <t>1 bild på låga samt garn i gran</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 35068-2025 artfynd.xlsx
+++ b/artfynd/A 35068-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127721543</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127721727</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127721889</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722108</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722196</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1339,6 +1369,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722396</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1451,8 +1486,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127721821</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>